--- a/tutorial_01/WS_DP849_DP846.xlsx
+++ b/tutorial_01/WS_DP849_DP846.xlsx
@@ -435,7 +435,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.21</t>
+          <t>Created with PyAnalyseries v5.22</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
   <dimension ref="A1:L698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -6139,8 +6139,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="173" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -30574,8 +30574,8 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -30875,8 +30875,8 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -53868,8 +53868,8 @@
   <dimension ref="A1:L1242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -53877,8 +53877,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="173" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -90442,7 +90442,7 @@
   <dimension ref="A1:L698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -90451,8 +90451,8 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="173" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -98392,7 +98392,7 @@
   <dimension ref="A1:L698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -98401,9 +98401,9 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="327" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/tutorial_01/WS_DP849_DP846.xlsx
+++ b/tutorial_01/WS_DP849_DP846.xlsx
@@ -435,7 +435,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Created with PyAnalyseries v5.23</t>
+          <t>Created with PyAnalyseries v5.25</t>
         </is>
       </c>
     </row>
@@ -98392,11 +98392,11 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>#ff7f0e</t>
+          <t>#60ff3c</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
